--- a/amostras/amostras_xlsx/Pesquisa_Eleitoral_Amostra_1.xlsx
+++ b/amostras/amostras_xlsx/Pesquisa_Eleitoral_Amostra_1.xlsx
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>Flávio Bolsonaro (PL)</t>
-  </si>
-  <si>
-    <t>Femenino</t>
   </si>
   <si>
     <t>SR</t>
@@ -324,7 +321,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -339,10 +336,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
@@ -362,7 +359,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>4</v>
@@ -385,7 +382,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>4</v>
@@ -408,7 +405,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>4</v>
@@ -431,7 +428,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>4</v>
@@ -454,7 +451,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>4</v>
@@ -462,22 +459,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>4</v>
@@ -485,22 +482,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>4</v>
@@ -508,22 +505,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>4</v>
@@ -531,22 +528,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>4</v>
@@ -554,22 +551,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>4</v>
@@ -583,16 +580,16 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>4</v>
@@ -609,13 +606,13 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>4</v>
@@ -629,16 +626,16 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>4</v>
@@ -652,16 +649,16 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>4</v>
@@ -669,22 +666,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>16</v>
-      </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>4</v>
@@ -692,22 +689,22 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>4</v>
@@ -730,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>4</v>
@@ -744,16 +741,16 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -767,16 +764,16 @@
         <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>4</v>
@@ -793,13 +790,13 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>4</v>
@@ -807,22 +804,22 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>4</v>
@@ -833,19 +830,19 @@
         <v>5</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>4</v>
@@ -859,16 +856,16 @@
         <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>4</v>
@@ -876,22 +873,22 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>16</v>
-      </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>4</v>
@@ -908,13 +905,13 @@
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>4</v>
@@ -928,16 +925,16 @@
         <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>4</v>
@@ -945,7 +942,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
@@ -954,13 +951,13 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>4</v>
@@ -968,7 +965,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
@@ -977,13 +974,13 @@
         <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>4</v>
@@ -997,16 +994,16 @@
         <v>7</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>4</v>
@@ -1020,16 +1017,16 @@
         <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>4</v>
@@ -1043,16 +1040,16 @@
         <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
         <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>4</v>
@@ -1060,7 +1057,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
@@ -1069,13 +1066,13 @@
         <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>4</v>
@@ -1083,22 +1080,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>4</v>
@@ -1109,19 +1106,19 @@
         <v>5</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>4</v>
@@ -1129,22 +1126,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>4</v>
@@ -1152,7 +1149,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
@@ -1161,13 +1158,13 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>4</v>
@@ -1175,7 +1172,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
@@ -1184,13 +1181,13 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>4</v>
@@ -1204,16 +1201,16 @@
         <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>4</v>
@@ -1221,7 +1218,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
@@ -1230,13 +1227,13 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" t="s">
         <v>26</v>
       </c>
-      <c r="E51" t="s">
-        <v>27</v>
-      </c>
       <c r="F51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>4</v>
@@ -1250,16 +1247,16 @@
         <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D53" t="s">
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>4</v>
@@ -1267,22 +1264,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>4</v>
@@ -1296,16 +1293,16 @@
         <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>4</v>
@@ -1313,22 +1310,22 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>4</v>
@@ -1336,22 +1333,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>4</v>
@@ -1365,16 +1362,16 @@
         <v>7</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>4</v>
@@ -1397,7 +1394,7 @@
         <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>4</v>
@@ -1405,7 +1402,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
@@ -1414,13 +1411,13 @@
         <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>4</v>
@@ -1437,13 +1434,13 @@
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>4</v>
@@ -1457,16 +1454,16 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>4</v>
@@ -1483,13 +1480,13 @@
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>4</v>
@@ -1497,7 +1494,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
@@ -1506,13 +1503,13 @@
         <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>4</v>
@@ -1529,13 +1526,13 @@
         <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>4</v>
@@ -1549,16 +1546,16 @@
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>4</v>
@@ -1572,16 +1569,16 @@
         <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>4</v>
@@ -1595,16 +1592,16 @@
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D78" t="s">
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>4</v>
@@ -1612,22 +1609,22 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C79" t="s">
         <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>4</v>
@@ -1638,7 +1635,7 @@
         <v>5</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
@@ -1647,10 +1644,10 @@
         <v>8</v>
       </c>
       <c r="E80" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>4</v>
@@ -1658,22 +1655,22 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>4</v>
@@ -1687,16 +1684,16 @@
         <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D85" t="s">
         <v>8</v>
       </c>
       <c r="E85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>4</v>
@@ -1707,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C88" t="s">
         <v>6</v>
@@ -1716,10 +1713,10 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>4</v>
@@ -1733,16 +1730,16 @@
         <v>7</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D89" t="s">
         <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>4</v>
@@ -1750,7 +1747,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>7</v>
@@ -1759,13 +1756,13 @@
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>4</v>
@@ -1773,13 +1770,13 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
+        <v>28</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C91" t="s">
         <v>29</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C91" t="s">
-        <v>30</v>
       </c>
       <c r="D91" t="s">
         <v>9</v>
@@ -1788,7 +1785,7 @@
         <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>4</v>
@@ -1796,7 +1793,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>7</v>
@@ -1811,7 +1808,7 @@
         <v>10</v>
       </c>
       <c r="F92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>4</v>
@@ -1822,10 +1819,10 @@
         <v>5</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C93" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D93" t="s">
         <v>13</v>
@@ -1834,7 +1831,7 @@
         <v>10</v>
       </c>
       <c r="F93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>4</v>
@@ -1848,7 +1845,7 @@
         <v>7</v>
       </c>
       <c r="C94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D94" t="s">
         <v>13</v>
@@ -1857,7 +1854,7 @@
         <v>12</v>
       </c>
       <c r="F94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>4</v>
@@ -1865,7 +1862,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>7</v>
@@ -1874,13 +1871,13 @@
         <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F95" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>4</v>
@@ -1888,22 +1885,22 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F97" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>4</v>
@@ -1911,22 +1908,22 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D98" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>4</v>
@@ -1934,7 +1931,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>7</v>
@@ -1943,13 +1940,13 @@
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F99" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>4</v>
@@ -1963,16 +1960,16 @@
         <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D100" t="s">
         <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>4</v>
@@ -1980,22 +1977,22 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
+        <v>28</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" t="s">
         <v>29</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C101" t="s">
-        <v>30</v>
-      </c>
       <c r="D101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F101" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>4</v>
